--- a/Donnees/Statistiques Economiques/Énergie (2).xlsx
+++ b/Donnees/Statistiques Economiques/Énergie (2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Annuaire\Chapitres_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Economiques\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAFDCB5-D1AA-43F5-9B0F-A774669902CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB59CB27-F71F-4E2B-868D-6A570FCC2708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricité1" sheetId="8" r:id="rId1"/>
@@ -1409,24 +1409,11 @@
     <definedName name="Zone_impres_MI">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="60">
   <si>
     <t>S_theme</t>
   </si>
@@ -1456,9 +1443,6 @@
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>1 773 837</t>
   </si>
   <si>
     <t>Janvier</t>
@@ -1570,9 +1554,6 @@
   </si>
   <si>
     <t>81 313 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">92 497 </t>
   </si>
   <si>
     <t>Nouakchott</t>
@@ -31710,7 +31691,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="17">
         <v>1995</v>
@@ -31805,13 +31786,13 @@
     </row>
     <row r="2" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -31823,7 +31804,7 @@
         <v>9</v>
       </c>
       <c r="J2" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" s="40">
         <v>169796.97099999999</v>
@@ -31909,8 +31890,8 @@
       <c r="AL2" s="40">
         <v>1574720</v>
       </c>
-      <c r="AM2" s="41" t="s">
-        <v>10</v>
+      <c r="AM2" s="41">
+        <v>1773837</v>
       </c>
       <c r="AN2" s="41">
         <v>1770920</v>
@@ -31918,13 +31899,13 @@
     </row>
     <row r="3" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -31936,10 +31917,10 @@
         <v>1</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="29">
         <v>12542.700999999999</v>
@@ -32034,13 +32015,13 @@
     </row>
     <row r="4" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -32052,10 +32033,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K4" s="29">
         <v>12157.8</v>
@@ -32150,13 +32131,13 @@
     </row>
     <row r="5" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -32168,10 +32149,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K5" s="29">
         <v>12652.34</v>
@@ -32266,13 +32247,13 @@
     </row>
     <row r="6" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -32284,10 +32265,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K6" s="29">
         <v>12436.418</v>
@@ -32382,13 +32363,13 @@
     </row>
     <row r="7" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -32400,10 +32381,10 @@
         <v>1</v>
       </c>
       <c r="I7" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K7" s="29">
         <v>13414.221</v>
@@ -32498,13 +32479,13 @@
     </row>
     <row r="8" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -32516,10 +32497,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8" s="29">
         <v>13862.699000000001</v>
@@ -32614,13 +32595,13 @@
     </row>
     <row r="9" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -32632,10 +32613,10 @@
         <v>1</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K9" s="29">
         <v>15149.905000000001</v>
@@ -32728,13 +32709,13 @@
     </row>
     <row r="10" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -32746,10 +32727,10 @@
         <v>1</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K10" s="29">
         <v>15207.45</v>
@@ -32842,13 +32823,13 @@
     </row>
     <row r="11" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -32860,10 +32841,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K11" s="29">
         <v>16018.424000000001</v>
@@ -32956,13 +32937,13 @@
     </row>
     <row r="12" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -32974,10 +32955,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K12" s="29">
         <v>16620.07</v>
@@ -33070,13 +33051,13 @@
     </row>
     <row r="13" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -33088,10 +33069,10 @@
         <v>1</v>
       </c>
       <c r="I13" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K13" s="29">
         <v>15707.234</v>
@@ -33184,13 +33165,13 @@
     </row>
     <row r="14" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -33202,10 +33183,10 @@
         <v>1</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K14" s="29">
         <v>14027.709000000001</v>
@@ -33345,7 +33326,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="20">
         <v>1995</v>
@@ -33440,13 +33421,13 @@
     </row>
     <row r="2" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -33455,10 +33436,10 @@
         <v>1</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" s="29">
         <v>167982</v>
@@ -33544,8 +33525,8 @@
       <c r="AL2" s="29">
         <v>1574733</v>
       </c>
-      <c r="AM2" s="30" t="s">
-        <v>10</v>
+      <c r="AM2" s="30">
+        <v>1773837</v>
       </c>
       <c r="AN2" s="30">
         <v>1770920</v>
@@ -33553,13 +33534,13 @@
     </row>
     <row r="3" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -33571,10 +33552,10 @@
         <v>1</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="29">
         <v>101566</v>
@@ -33667,13 +33648,13 @@
     </row>
     <row r="4" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -33685,10 +33666,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K4" s="29">
         <v>56663</v>
@@ -33781,13 +33762,13 @@
     </row>
     <row r="5" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -33799,10 +33780,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K5" s="29">
         <v>9753</v>
@@ -33895,13 +33876,13 @@
     </row>
     <row r="6" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -33910,10 +33891,10 @@
         <v>5</v>
       </c>
       <c r="I6" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K6" s="29">
         <v>53</v>
@@ -34032,7 +34013,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="20">
         <v>1995</v>
@@ -34128,14 +34109,14 @@
     <row r="2" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="A2" s="27"/>
       <c r="B2" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="27"/>
       <c r="D2" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="27">
         <v>1</v>
@@ -34145,10 +34126,10 @@
       </c>
       <c r="H2" s="27"/>
       <c r="I2" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" s="29">
         <v>16168</v>
@@ -34229,13 +34210,13 @@
         <v>74100</v>
       </c>
       <c r="AK2" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AL2" s="30">
         <v>83451</v>
       </c>
-      <c r="AM2" s="30" t="s">
-        <v>48</v>
+      <c r="AM2" s="30">
+        <v>92497</v>
       </c>
       <c r="AN2" s="30">
         <v>99640</v>
@@ -34244,14 +34225,14 @@
     <row r="3" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="A3" s="27"/>
       <c r="B3" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="27"/>
       <c r="D3" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F3" s="27">
         <v>2</v>
@@ -34263,10 +34244,10 @@
         <v>1</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="29">
         <v>12660</v>
@@ -34350,14 +34331,14 @@
     <row r="4" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="A4" s="27"/>
       <c r="B4" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="27"/>
       <c r="D4" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="27" t="s">
         <v>57</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>59</v>
       </c>
       <c r="F4" s="27">
         <v>3</v>
@@ -34369,10 +34350,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K4" s="29">
         <v>2154</v>
@@ -34456,14 +34437,14 @@
     <row r="5" spans="1:40" ht="21.6" x14ac:dyDescent="0.65">
       <c r="A5" s="27"/>
       <c r="B5" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F5" s="27">
         <v>4</v>
@@ -34475,10 +34456,10 @@
         <v>1</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K5" s="29">
         <v>1354</v>
@@ -34610,43 +34591,43 @@
         <v>7</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="L2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>18</v>
-      </c>
       <c r="O2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="11" t="s">
+      <c r="R2" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="S2" s="11" t="s">
         <v>9</v>
@@ -34654,10 +34635,10 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -34684,10 +34665,10 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -34699,7 +34680,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" s="42">
         <v>27.56</v>
@@ -34743,10 +34724,10 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -34758,7 +34739,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" s="42">
         <v>11.69</v>
@@ -34802,10 +34783,10 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -34817,7 +34798,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" s="42">
         <v>15.87</v>
@@ -34861,10 +34842,10 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -34876,7 +34857,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
@@ -34894,10 +34875,10 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -34924,10 +34905,10 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -34939,7 +34920,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="42">
         <v>28.962266</v>
@@ -34983,10 +34964,10 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10">
         <v>8</v>
@@ -34998,7 +34979,7 @@
         <v>7</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" s="42">
         <v>11.530495999999999</v>
@@ -35042,10 +35023,10 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <v>9</v>
@@ -35057,7 +35038,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="42">
         <v>17.43177</v>
@@ -35101,10 +35082,10 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -35116,7 +35097,7 @@
         <v>6</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
@@ -35134,10 +35115,10 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <v>11</v>
@@ -35164,10 +35145,10 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A14" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -35179,7 +35160,7 @@
         <v>11</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="42">
         <v>32.642611000000002</v>
@@ -35223,10 +35204,10 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -35238,7 +35219,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" s="42">
         <v>11.991391</v>
@@ -35282,10 +35263,10 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16">
         <v>14</v>
@@ -35297,7 +35278,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16" s="42">
         <v>20.651219999999999</v>
@@ -35341,10 +35322,10 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A17" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17">
         <v>15</v>
@@ -35356,7 +35337,7 @@
         <v>11</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G17" s="42">
         <v>27.186</v>
@@ -35400,10 +35381,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18">
         <v>16</v>
@@ -35430,10 +35411,10 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C19">
         <v>17</v>
@@ -35445,7 +35426,7 @@
         <v>16</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="42">
         <v>35.92</v>
@@ -35489,10 +35470,10 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>18</v>
@@ -35504,7 +35485,7 @@
         <v>17</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" s="42">
         <v>13.01</v>
@@ -35548,10 +35529,10 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21">
         <v>19</v>
@@ -35563,7 +35544,7 @@
         <v>17</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G21" s="42">
         <v>22.91</v>
@@ -35607,10 +35588,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22">
         <v>20</v>
@@ -35622,7 +35603,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22" s="42">
         <v>26.863</v>
@@ -35658,7 +35639,7 @@
         <v>26.173999999999999</v>
       </c>
       <c r="R22" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S22" s="43">
         <v>297.84100000000001</v>
@@ -35666,10 +35647,10 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>21</v>
@@ -35696,10 +35677,10 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>22</v>
@@ -35711,7 +35692,7 @@
         <v>21</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24" s="42">
         <v>38.776265000000002</v>
@@ -35755,10 +35736,10 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>23</v>
@@ -35770,7 +35751,7 @@
         <v>22</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G25" s="42">
         <v>14.397</v>
@@ -35814,10 +35795,10 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>24</v>
@@ -35829,7 +35810,7 @@
         <v>22</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G26" s="42">
         <v>24.379265</v>
@@ -35873,10 +35854,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>25</v>
@@ -35888,54 +35869,54 @@
         <v>21</v>
       </c>
       <c r="F27" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="42" t="s">
-        <v>35</v>
-      </c>
       <c r="H27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S27" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>26</v>
@@ -35962,10 +35943,10 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>27</v>
@@ -35977,7 +35958,7 @@
         <v>26</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" s="42">
         <v>40.86</v>
@@ -36021,10 +36002,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>28</v>
@@ -36036,7 +36017,7 @@
         <v>27</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30" s="42">
         <v>14.83</v>
@@ -36080,10 +36061,10 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A31" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>29</v>
@@ -36095,7 +36076,7 @@
         <v>27</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G31" s="42">
         <v>26.03</v>
@@ -36139,10 +36120,10 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C32">
         <v>30</v>
@@ -36154,7 +36135,7 @@
         <v>26</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G32" s="42">
         <v>24.611999999999998</v>
@@ -36198,10 +36179,10 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A33" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C33">
         <v>31</v>
@@ -36228,10 +36209,10 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A34" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C34">
         <v>32</v>
@@ -36243,7 +36224,7 @@
         <v>31</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G34" s="42">
         <v>44.27</v>
@@ -36287,10 +36268,10 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A35" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C35">
         <v>33</v>
@@ -36302,7 +36283,7 @@
         <v>32</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G35" s="42">
         <v>16.760000000000002</v>
@@ -36346,10 +36327,10 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C36">
         <v>34</v>
@@ -36361,7 +36342,7 @@
         <v>32</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G36" s="42">
         <v>27.51</v>
@@ -36405,10 +36386,10 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -36420,7 +36401,7 @@
         <v>31</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G37" s="42">
         <v>28.791</v>
@@ -36464,10 +36445,10 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A38" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C38">
         <v>36</v>
@@ -36494,10 +36475,10 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39">
         <v>37</v>
@@ -36509,7 +36490,7 @@
         <v>36</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39" s="42">
         <v>47.36</v>
@@ -36553,10 +36534,10 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A40" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C40">
         <v>38</v>
@@ -36568,7 +36549,7 @@
         <v>37</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G40" s="42">
         <v>19</v>
@@ -36612,10 +36593,10 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C41">
         <v>39</v>
@@ -36627,7 +36608,7 @@
         <v>37</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G41" s="42">
         <v>28.36</v>
@@ -36671,10 +36652,10 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A42" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C42">
         <v>40</v>
@@ -36686,7 +36667,7 @@
         <v>36</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G42" s="42">
         <v>29.64</v>
@@ -36730,10 +36711,10 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C43">
         <v>41</v>
@@ -36760,10 +36741,10 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C44">
         <v>42</v>
@@ -36775,7 +36756,7 @@
         <v>41</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G44" s="42">
         <v>50.909492999999998</v>
@@ -36819,10 +36800,10 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C45">
         <v>43</v>
@@ -36834,7 +36815,7 @@
         <v>42</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G45" s="42">
         <v>21.742815</v>
@@ -36878,10 +36859,10 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C46">
         <v>44</v>
@@ -36893,7 +36874,7 @@
         <v>42</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G46" s="42">
         <v>29.166678000000001</v>
@@ -36937,10 +36918,10 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>45</v>
@@ -36952,7 +36933,7 @@
         <v>41</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G47" s="42">
         <v>28.475999999999999</v>
@@ -36996,10 +36977,10 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A48" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C48">
         <v>46</v>
@@ -37026,10 +37007,10 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A49" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C49">
         <v>47</v>
@@ -37041,7 +37022,7 @@
         <v>46</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G49" s="42">
         <v>56.7</v>
@@ -37085,10 +37066,10 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C50">
         <v>48</v>
@@ -37100,7 +37081,7 @@
         <v>47</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G50" s="42">
         <v>24.14</v>
@@ -37144,10 +37125,10 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A51" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C51">
         <v>49</v>
@@ -37159,7 +37140,7 @@
         <v>47</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G51" s="42">
         <v>32.56</v>
@@ -37203,10 +37184,10 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C52">
         <v>50</v>
@@ -37218,7 +37199,7 @@
         <v>46</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G52" s="42">
         <v>28.145</v>
@@ -37262,10 +37243,10 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A53" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C53">
         <v>51</v>
@@ -37292,10 +37273,10 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A54" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C54">
         <v>52</v>
@@ -37307,7 +37288,7 @@
         <v>51</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G54" s="42">
         <v>59.97</v>
@@ -37351,10 +37332,10 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A55" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C55">
         <v>53</v>
@@ -37366,7 +37347,7 @@
         <v>52</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G55" s="42">
         <v>25.55</v>
@@ -37410,10 +37391,10 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A56" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C56">
         <v>54</v>
@@ -37425,7 +37406,7 @@
         <v>52</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G56" s="42">
         <v>34.42</v>
@@ -37469,10 +37450,10 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A57" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C57">
         <v>55</v>
@@ -37484,7 +37465,7 @@
         <v>51</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G57" s="42">
         <v>29.835999999999999</v>
@@ -37528,10 +37509,10 @@
     </row>
     <row r="58" spans="1:19" ht="30" x14ac:dyDescent="0.85">
       <c r="A58" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C58">
         <v>56</v>
@@ -37558,10 +37539,10 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A59" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C59">
         <v>57</v>
@@ -37573,7 +37554,7 @@
         <v>56</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G59" s="42">
         <v>72.3</v>
@@ -37617,10 +37598,10 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A60" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B60" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C60">
         <v>58</v>
@@ -37632,7 +37613,7 @@
         <v>57</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G60" s="42">
         <v>35.04</v>
@@ -37676,10 +37657,10 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A61" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B61" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C61">
         <v>59</v>
@@ -37691,7 +37672,7 @@
         <v>57</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G61" s="42">
         <v>37.26</v>
@@ -37735,10 +37716,10 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A62" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B62" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C62">
         <v>60</v>
@@ -37750,7 +37731,7 @@
         <v>56</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G62" s="42">
         <v>27.227</v>
@@ -37794,10 +37775,10 @@
     </row>
     <row r="63" spans="1:19" ht="30" x14ac:dyDescent="0.85">
       <c r="A63" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B63" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63">
         <v>61</v>
@@ -37824,10 +37805,10 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A64" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B64" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C64">
         <v>62</v>
@@ -37839,7 +37820,7 @@
         <v>61</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G64" s="42">
         <v>72.5</v>
@@ -37883,10 +37864,10 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A65" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C65">
         <v>63</v>
@@ -37898,7 +37879,7 @@
         <v>62</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G65" s="42">
         <v>35.1</v>
@@ -37942,10 +37923,10 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A66" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C66">
         <v>64</v>
@@ -37957,7 +37938,7 @@
         <v>62</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G66" s="42">
         <v>37.5</v>
@@ -38001,10 +37982,10 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A67" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B67" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C67">
         <v>65</v>
@@ -38016,7 +37997,7 @@
         <v>61</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G67" s="42">
         <v>29.148</v>
@@ -38042,10 +38023,10 @@
     </row>
     <row r="68" spans="1:19" ht="30" x14ac:dyDescent="0.85">
       <c r="A68" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B68" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C68">
         <v>66</v>
@@ -38072,10 +38053,10 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A69" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B69" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C69">
         <v>67</v>
@@ -38087,7 +38068,7 @@
         <v>66</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G69" s="42">
         <v>72.7</v>
@@ -38131,10 +38112,10 @@
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A70" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B70" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C70">
         <v>68</v>
@@ -38146,7 +38127,7 @@
         <v>67</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G70" s="42">
         <v>33.9</v>
@@ -38190,10 +38171,10 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A71" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B71" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C71">
         <v>69</v>
@@ -38205,7 +38186,7 @@
         <v>67</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G71" s="42">
         <v>38.799999999999997</v>
@@ -38249,10 +38230,10 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A72" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B72" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C72">
         <v>70</v>
@@ -38264,7 +38245,7 @@
         <v>66</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G72" s="42"/>
       <c r="H72" s="42"/>
@@ -38282,10 +38263,10 @@
     </row>
     <row r="73" spans="1:19" ht="30" x14ac:dyDescent="0.85">
       <c r="A73" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B73" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C73">
         <v>71</v>
@@ -38312,10 +38293,10 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A74" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C74">
         <v>72</v>
@@ -38327,7 +38308,7 @@
         <v>71</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G74" s="42">
         <v>85.43</v>
@@ -38371,10 +38352,10 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A75" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C75">
         <v>73</v>
@@ -38386,7 +38367,7 @@
         <v>72</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G75" s="42">
         <v>40.85</v>
@@ -38430,10 +38411,10 @@
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A76" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C76">
         <v>74</v>
@@ -38445,7 +38426,7 @@
         <v>72</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G76" s="42">
         <v>44.58</v>
@@ -38489,10 +38470,10 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.7">
       <c r="A77" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C77">
         <v>75</v>
@@ -38504,7 +38485,7 @@
         <v>71</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
@@ -38584,7 +38565,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="21">
         <v>2010</v>
@@ -38634,13 +38615,13 @@
     </row>
     <row r="2" spans="1:25" ht="27" x14ac:dyDescent="0.75">
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -38649,10 +38630,10 @@
         <v>1</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2" s="33">
         <v>655</v>
@@ -38702,13 +38683,13 @@
     </row>
     <row r="3" spans="1:25" ht="27" x14ac:dyDescent="0.75">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -38720,10 +38701,10 @@
         <v>1</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="33">
         <v>630.5</v>
@@ -38773,13 +38754,13 @@
     </row>
     <row r="4" spans="1:25" ht="27" x14ac:dyDescent="0.75">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -38791,10 +38772,10 @@
         <v>2</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K4" s="35">
         <v>25</v>
@@ -38844,13 +38825,13 @@
     </row>
     <row r="5" spans="1:25" ht="27" x14ac:dyDescent="0.75">
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -38862,10 +38843,10 @@
         <v>2</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K5" s="35">
         <v>159.80000000000001</v>
@@ -38915,13 +38896,13 @@
     </row>
     <row r="6" spans="1:25" ht="27" x14ac:dyDescent="0.75">
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -38933,10 +38914,10 @@
         <v>2</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K6" s="35">
         <v>17.600000000000001</v>
@@ -38986,13 +38967,13 @@
     </row>
     <row r="7" spans="1:25" ht="27" x14ac:dyDescent="0.75">
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -39004,10 +38985,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K7" s="35">
         <v>428.1</v>
@@ -39057,13 +39038,13 @@
     </row>
     <row r="8" spans="1:25" ht="27" x14ac:dyDescent="0.75">
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -39075,10 +39056,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8" s="35">
         <v>24.5</v>
